--- a/source-excel/Pointsdeducted.xlsx
+++ b/source-excel/Pointsdeducted.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\รายงานการจัดระดับ\ข้อมูลทำ AI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\รายงานการจัดระดับ\newstarrating\source-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FCC0337-BE14-4D4E-95CA-B76340AFE7BF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0ECD30F-A44F-4453-8B26-DACF1166CE26}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8130" xr2:uid="{20C5A273-AF55-44C0-B9FD-8786E546917F}"/>
   </bookViews>
@@ -72,9 +72,6 @@
     <t>FC214</t>
   </si>
   <si>
-    <t>สระกระโจม</t>
-  </si>
-  <si>
     <t>FC248</t>
   </si>
   <si>
@@ -84,9 +81,6 @@
     <t>FC299</t>
   </si>
   <si>
-    <t xml:space="preserve">เนินพระปรางค์ </t>
-  </si>
-  <si>
     <t>4-North</t>
   </si>
   <si>
@@ -166,6 +160,12 @@
   </si>
   <si>
     <t>มีข้อร้องเรียน</t>
+  </si>
+  <si>
+    <t>ดอนเจดีย์</t>
+  </si>
+  <si>
+    <t>สองพี่น้อง 2</t>
   </si>
 </sst>
 </file>
@@ -617,10 +617,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="17.5" thickBot="1">
@@ -683,7 +683,7 @@
         <v>14</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
@@ -693,10 +693,10 @@
         <v>13</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
@@ -706,153 +706,153 @@
         <v>13</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
     </row>
     <row r="9" spans="1:5" ht="17.5" thickBot="1">
       <c r="A9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
     </row>
     <row r="10" spans="1:5" ht="17.5" thickBot="1">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
     </row>
     <row r="11" spans="1:5" ht="17.5" thickBot="1">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
     </row>
     <row r="12" spans="1:5" ht="17.5" thickBot="1">
       <c r="A12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
     </row>
     <row r="13" spans="1:5" ht="17.5" thickBot="1">
       <c r="A13" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
     </row>
     <row r="14" spans="1:5" ht="17.5" thickBot="1">
       <c r="A14" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
     </row>
     <row r="15" spans="1:5" ht="17.5" thickBot="1">
       <c r="A15" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
     </row>
     <row r="16" spans="1:5" ht="17.5" thickBot="1">
       <c r="A16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
     </row>
     <row r="17" spans="1:5" ht="17.5" thickBot="1">
       <c r="A17" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
     </row>
     <row r="18" spans="1:5" ht="17.5" thickBot="1">
       <c r="A18" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
     </row>
     <row r="19" spans="1:5" ht="17.5" thickBot="1">
       <c r="A19" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
